--- a/robotai_BOM.xlsx
+++ b/robotai_BOM.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="&quot;US$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -133,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -194,13 +193,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1869,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1884,14 +1876,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Phase 2 - bimanual mobile robot (XLeRobot-style), PRICES IN USD</t>
+          <t>Phase 2 - Life-size humanoid v1 (torso + arms on a wheeled base), Kimi round 3 - prices in CAD</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>From research/physical_ai_research.md s.6. Separate from the $500 CAD hands budget. Prices from vendor pages/coverage on 2026-09-25.</t>
+          <t>Total C$1,341.49 pre-tax vs the C$1,500 budget (C$158.51 buffer). Compute is the owner's laptop (Pi Zero 2 W is out of stock in Canada). Week 1: buy ONE 1000:1 and ONE 500:1 motor and bench-test them (torque 80 kg-cm, backlash &lt;= 1.5 deg, self-lock &lt; 1 deg, &lt; 60 C) before ordering the other six. Legs gate at week 10: two more STS3215 6-packs + 3S LiPo (~C$388) for the small walker; needs trims of ~C$229 from the buffer.</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1915,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Unit Price (USD)</t>
+          <t>Unit Price (CAD)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1933,7 +1925,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Line Total (USD)</t>
+          <t>Line Total (CAD)</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -1945,197 +1937,613 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>SO-ARM101 Pro motor kit (leader+follower servos, driver, cables)</t>
+          <t>Shoulder pitch + roll motors (x4)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Seeed Studio</t>
+          <t>NFP 5840-31ZY-EN 12V worm motor, 1000:1, hall encoder</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>https://www.seeedstudio.com/SO-101-Low-Cost-AI-Arm-Kit-Pro-p-6427.html</t>
-        </is>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>249.9</v>
+          <t>https://nfpmotor.com/12v-24v-dc-permanent-magnet-dc-turbo-worm-reduction-motor-model-nfp-5840-31zy</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>79</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="31">
+        <v>4</v>
+      </c>
+      <c r="F6" s="13">
         <f>D6*E6</f>
         <v/>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Core arm. 2 kits = bimanual. STS3215 bus servos. LeRobot-native.</t>
+          <t>100 kg-cm rated (1.4x margin on 71 kg-cm needed), ~2.5 s per 90 deg, self-locking so arms hold without power. AliExpress regular price C$79 (C$30 promo is 1 per customer). Buy 1 first and bench-test.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>SO-101 printed parts</t>
+          <t>Shoulder yaw + elbow motors (x4)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Seeed Studio (or print yourself = $0)</t>
+          <t>NFP 5840-31ZY-EN 12V worm motor, 500:1, hall encoder</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>https://www.seeedstudio.com/SO-101-Low-Cost-AI-Arm-Kit-Pro-p-6427.html</t>
-        </is>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>0</v>
+          <t>https://microdcmotors.com/product/12v-24v-high-torque-low-speed-dc-motor-with-encoder-self-locking-model-nfp-5840-31zy-en</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>79</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="31">
+        <v>4</v>
+      </c>
+      <c r="F7" s="13">
         <f>D7*E7</f>
         <v/>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>3D printing is covered, so $0. Seeed sells printed sets at $29.90 if needed.</t>
+          <t>70 kg-cm rated; elbow needs ~44 (1.6x), yaw ~25 (2.8x); ~1.25 s per 90 deg. Order after the week-1 bench test passes.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Mobile base (LeKiwi base, or DIY XLeRobot IKEA cart)</t>
+          <t>Wrist x2, neck x2, 2 spares</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>AIFITLAB LeKiwi</t>
+          <t>Feetech STS3215 12V 30 kg-cm bus servo, 6-pack (official store)</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>https://aifitlab.com/products/lerobot-lekiwi-low-cost-mobile-manipulator</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>260</v>
+          <t>https://www.aliexpress.com/item/1005008670304643.html</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>166.42</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="13">
         <f>D8*E8</f>
         <v/>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>'from $260'. XLeRobot full BOM ~$660 incl. arms: https://github.com/Vector-Wangel/XLeRobot</t>
+          <t>C$160.99 + C$5.43 shipping, 4.9 stars, 232 sold. Checked on the page.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>USB cameras (head + 2 wrist)</t>
+          <t>Drive base</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Seeed X10 USB camera</t>
+          <t>Used hoverboard (2x 350 W hub motors + 36 V pack)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>https://www.seeedstudio.com/LeKiwi-Full-Kit-12V-Verision.html</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="n">
-        <v>12</v>
+          <t>https://www.kijiji.ca/b-city-of-toronto/hoverboard/k0c170l1700273</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>120</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="31">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13">
         <f>D9*E9</f>
         <v/>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Listed as LeKiwi add-on.</t>
+          <t>C$50-150 on Kijiji Toronto (43 ads). Open it before paying: single mainboard with STM32F103RCT6/RET6 or GD32F103RCT6 only; walk away from AT32F403/413 boards. Runs EFeru FOC firmware (free).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>On-robot compute</t>
+          <t>Base power converter</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>NVIDIA Jetson Orin Nano Super Dev Kit</t>
+          <t>DC-DC buck 30-60 V in -&gt; 12 V, 15 A+</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>https://jetsonhacks.com/2024/12/17/jetson-orin-nano-super-developer-kit/</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>249</v>
+          <t>https://www.amazon.ca/</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>40</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="13">
         <f>D10*E10</f>
         <v/>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Runs ACT/SmolVLA locally. Skip and use a laptop to save $249.</t>
+          <t>Estimate C$35-45. Must accept 42 V (a 36 V pack charges to 42 V), so an 18-36 V input unit will fail.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Phase 2 subtotal (USD, pre-tax/shipping)</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="32">
-        <f>SUM(F6:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="15" t="n"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Casters (x2)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>2 in swivel casters</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Estimate. Stabilize the tall torso on the hoverboard base.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Phase 2 subtotal (CAD, approx.)</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="16">
-        <f>F11*$D$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="15" t="n"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Safety + power wiring</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>E-stop button, fuses, XT60 connectors, 14 AWG wire</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="13">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Estimate. Non-negotiable for a 1.8 m robot on wheels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Motor drivers (x8)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>BTS7960 43 A H-bridge</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>https://www.universal-solder.ca/product/dual-bts7960-h-bridge-dc-motor-driver-max-43a/</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="13">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>C$7.99, C$7.19 each at qty 3-9, in stock in Canada (Universal-Solder). Checked on the page.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Joint angle sensors (x8)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>AS5600 magnetic encoder module</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/w/wholesale-as5600-module.html</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="13">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Absolute angle on each worm-motor output shaft. Search-page price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Servo bus adapters (x2)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Waveshare Bus Servo Adapter (A)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>https://www.waveshare.com/bus-servo-adapter-a.htm</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="13">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>US$4.99 on waveshare.com; Canada shipping not checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Head camera</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>EMEET C960 1080p webcam</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07M6Y7355</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="13">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>4.4 stars, 32.5K ratings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Wrist cameras (x2)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>1080p UVC wide-angle camera module</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/w/wholesale-wide-angle-usb-camera.html</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="13">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Estimate. Can wait until week 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Balance / motion sensor</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>BNO085 9-axis IMU (clone)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/w/wholesale-bno085.html</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="13">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Adafruit original is C$33-40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Servo cables (x2 packs)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>5264 3-pin bus servo cable, 10-pack</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/item/1005008074862037.html</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="13">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>+ ~C$8 shipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Powered USB hub</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>7-port powered USB 3.0 hub (TP-Link UH700 class)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B00OTK16FK</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Checked: C$59-71 for reputable hubs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>M2/M3/M4 screw kit + 100 M3 heat-set inserts</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>LuKaiSen kit C$15.99 + HANGLIFE inserts C$10.99.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Work stand clamps</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>WEN CLC424 C-clamps, 2-pack</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B08SQFT9TW</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="13">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Holds the torso on the bench during arm bring-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Wire + connectors</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Assorted wire, JST/Dupont, heat shrink</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="13">
+        <f>D23*E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Phase 2 subtotal (CAD, pre-tax/shipping)</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="16">
+        <f>SUM(F6:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Under the C$1,500 budget by</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="16">
+        <f>1500-F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>Cerebras = System-2 brain (planner, voice, replanning, success checks) in the cloud; ACT/SmolVLA motor policy runs locally at 30-50 Hz. See research brief.</t>
         </is>
@@ -2143,8 +2551,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A24:E24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId1"/>
@@ -2152,6 +2560,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/robotai_BOM.xlsx
+++ b/robotai_BOM.xlsx
@@ -1861,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1876,14 +1876,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Phase 2 - Life-size humanoid v1 (torso + arms on a wheeled base), Kimi round 3 - prices in CAD</t>
+          <t>Phase 2 - Life-size InMoov humanoid v1 (both arms on stock InMoov STLs + wheeled base) - prices in CAD</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total C$1,341.49 pre-tax vs the C$1,500 budget (C$158.51 buffer). Compute is the owner's laptop (Pi Zero 2 W is out of stock in Canada). Week 1: buy ONE 1000:1 and ONE 500:1 motor and bench-test them (torque 80 kg-cm, backlash &lt;= 1.5 deg, self-lock &lt; 1 deg, &lt; 60 C) before ordering the other six. Legs gate at week 10: two more STS3215 6-packs + 3S LiPo (~C$388) for the small walker; needs trims of ~C$229 from the buffer.</t>
+          <t>Both arms C$452.30 pre-tax (cap C$500). Whole phase 2 C$1077.15; plus the hands cart (already bought) C$316.40. Arm servos per arm: omoplate, rotate, bicep = DS5160 60 kg with the pot moved to the joint (Gael's mod); shoulder = DS5160 pot in place, limited 0-80; wrist + 5 fingers = owned MG996R. DS5160 is the HS-805BB footprint (65x30 mm) but 10 mm shorter: expect a printed spacer under the tabs; test-fit one before printing everything. Exact drop-in is the PDI-HV2060MG (~C$54 each, would break the cap). Removed vs round 3: 8x NFP 5840 worm motors, 8x BTS7960, 8x AS5600 (custom-arm parts that don't mount in InMoov STLs). The owned PCA9685s drive the arm servos.</t>
         </is>
       </c>
     </row>
@@ -1937,24 +1937,24 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Shoulder pitch + roll motors (x4)</t>
+          <t>ARM: Big arm servos (omoplate, shoulder, rotate, bicep x 2 arms)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>NFP 5840-31ZY-EN 12V worm motor, 1000:1, hall encoder</t>
+          <t>DS5160 SSG 60 kg HV digital servo, 180deg variant (RC Toys Upgrade Haven Store, 4.9 stars, 471 sold)</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>https://nfpmotor.com/12v-24v-dc-permanent-magnet-dc-turbo-worm-reduction-motor-model-nfp-5840-31zy</t>
+          <t>https://www.aliexpress.com/item/1005005676958064.html</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>79</v>
+        <v>32.84</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="13">
         <f>D6*E6</f>
@@ -1962,31 +1962,31 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>100 kg-cm rated (1.4x margin on 71 kg-cm needed), ~2.5 s per 90 deg, self-locking so arms hold without power. AliExpress regular price C$79 (C$30 promo is 1 per customer). Buy 1 first and bench-test.</t>
+          <t>ALIEXPRESS, FLAGGED: Amazon.ca DS5160 listings are C$50-57 each (one visible at C$56.75), so 8 of them would take C$400-450 of the C$500 cap. AliExpress shows free shipping. Pick the 180deg variant, not 270. 58 kg-cm at 6 V / 70 kg-cm at 8.4 V, about 2.5x an HS-805BB. The price could be a first-order deal, so re-check it in the cart. Amazon.ca fallback: ANNIMOS 60KG B07KTSCN4J (194 ratings), ZOSKAY B07K48FQ1N (85), 2-pack B09JGBW9KZ. [verified-on-page (AliExpress item page, C$32.84, free shipping)]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Shoulder yaw + elbow motors (x4)</t>
+          <t>ARM: Arm servo power (one per arm, set to 7.4 V)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>NFP 5840-31ZY-EN 12V worm motor, 500:1, hall encoder</t>
+          <t>SHNITPWR 3.5-12V adjustable 12A 144W PSU</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>https://microdcmotors.com/product/12v-24v-high-torque-low-speed-dc-motor-with-encoder-self-locking-model-nfp-5840-31zy-en</t>
+          <t>https://www.amazon.ca/dp/B0CKXW6ZCJ</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>79</v>
+        <v>36.79</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="13">
         <f>D7*E7</f>
@@ -1994,28 +1994,28 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>70 kg-cm rated; elbow needs ~44 (1.6x), yaw ~25 (2.8x); ~1.25 s per 90 deg. Order after the week-1 bench test passes.</t>
+          <t>Same family as the hand PSUs you already own. Each one runs the 4 big servos of one arm. The worm joints hold their position with the power off, so only 1-2 servos load up at a time. Gael runs a single 6 V 40-60 A supply for the whole robot; splitting per arm means one supply can't brown out the whole robot. Alternative: Aclorol 5V 60A B07KC3KSHP at C$51.38 (verified on the search page), but it only reaches about 5.5 V. [price from the existing bom.json alternatives (earlier check), not re-verified today because Amazon.ca hides prices on a Santa Clara address]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Wrist x2, neck x2, 2 spares</t>
+          <t>ARM: M3/M4 countersunk bolts + nuts</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Feetech STS3215 12V 30 kg-cm bus servo, 6-pack (official store)</t>
+          <t>DYWISHKEY 500pcs M3 M4 M5 304 stainless flat-head countersunk socket cap screws + nuts</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/item/1005008670304643.html</t>
+          <t>https://www.amazon.ca/dp/B08QD6TT2N</t>
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>166.42</v>
+        <v>35.47</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1</v>
@@ -2026,28 +2026,28 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>C$160.99 + C$5.43 shipping, 4.9 stars, 232 sold. Checked on the page.</t>
+          <t>InMoov BOM calls for about 50x M3x20 and 50x M4x20 countersunk, plus M3 nuts. Check the kit goes up to 20 mm (the thesis lists 3 mm screws at 12/20/30/35 mm). This overlaps the phase2 'Hardware' line (LuKaiSen kit C$15.99); you can drop that kit's screws and keep only the heat-set inserts. [verified on the Amazon.ca search results page (C$35.47, 55 ratings)]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Drive base</t>
+          <t>ARM: Spare 10k pots for the pot-relocation mod</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Used hoverboard (2x 350 W hub motors + 36 V pack)</t>
+          <t>uxcell WH148 10K rotary potentiometer, 10 pcs</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/b-city-of-toronto/hoverboard/k0c170l1700273</t>
+          <t>https://www.amazon.ca/dp/B07JM62B3Q</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>120</v>
+        <v>13.99</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>1</v>
@@ -2058,28 +2058,28 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>C$50-150 on Kijiji Toronto (43 ads). Open it before paying: single mainboard with STM32F103RCT6/RET6 or GD32F103RCT6 only; walk away from AT32F403/413 boards. Runs EFeru FOC firmware (free).</t>
+          <t>The first choice is to reuse each servo's own pot on an extension lead (Gael: cut the wires and splice in length, don't desolder at the PCB). Builders break these pots by over-rotating them, so spares are needed. The pot works as a voltage divider, so a 10k pot replacing a ~5k pot still works. Gael uses round pots (PivPotentioRound) and a square version exists; a WH148 needs a holder like Thingiverse thing:6923985 (shoulder, metal linear pot) or thing:1464929 (bicep, square pot). The listing title says 'Dual'; if it turns out to be dual-gang, use one gang. [verified on the Amazon.ca search results page (C$13.99); single vs dual gang not confirmed]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Base power converter</t>
+          <t>ARM: 6 mm BBs for the shoulder/rotate ball races</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>DC-DC buck 30-60 V in -&gt; 12 V, 15 A+</t>
+          <t>Lancer Tactical 0.20 g 6 mm BBs, 4000-round bag</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/</t>
+          <t>https://www.amazon.ca/dp/B00HC1U0LO</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>1</v>
@@ -2090,31 +2090,31 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Estimate C$35-45. Must accept 42 V (a 36 V pack charges to 42 V), so an 18-36 V input unit will fail.</t>
+          <t>Per arm: PivCenter 27 + PivMit 31 + RotCenter 27 + RotMit 31 = 116 balls, so 232 for both arms. The classic InMoov arm needs no other ball bearings. Gael warns that some greases dissolve plastic BBs, so use PTFE/silicone grease only. Canadian Tire sells the same BBs for about the same price. [estimate (Amazon.ca hides the price for this delivery address)]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Casters (x2)</t>
+          <t>ARM: Servo extension leads (pot relocation + reaching the PCA9685)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2 in swivel casters</t>
+          <t>10pc 30cm 3-pin servo extension cable (JR, F-M)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/</t>
+          <t>https://www.amazon.ca/dp/B09VGDJ6Z8</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>20</v>
+        <v>8.27</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="13">
         <f>D11*E11</f>
@@ -2122,28 +2122,28 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Estimate. Stabilize the tall torso on the hoverboard base.</t>
+          <t>3 relocated pots per arm need 25-35 cm leads, plus the 8 big servos need to reach the controller. Same SKU as the phase1 cart. [price from phase1 bom.json (earlier check)]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Safety + power wiring</t>
+          <t>ARM: Servo mounting wood screws</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>E-stop button, fuses, XT60 connectors, 14 AWG wire</t>
+          <t>Self-tapping screw assortment incl. M3x12 and 3.5x16 mm (4 per big servo)</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/</t>
+          <t>https://www.amazon.ca/s?k=self+tapping+screw+assortment+m3</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1</v>
@@ -2154,31 +2154,31 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Estimate. Non-negotiable for a 1.8 m robot on wheels.</t>
+          <t>InMoov BOM: about 100x M3x12 for small servos and about 50x M4x20 for large servos. Use a hardware store if that's cheaper. [estimate]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Motor drivers (x8)</t>
+          <t>ARM: M8 through-bolts</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>BTS7960 43 A H-bridge</t>
+          <t>M8x90-100 mm bolts + nylock nuts (about 6)</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>https://www.universal-solder.ca/product/dual-bts7960-h-bridge-dc-motor-driver-max-43a/</t>
+          <t>https://www.homedepot.ca/</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>7.19</v>
+        <v>15</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F13" s="13">
         <f>D13*E13</f>
@@ -2186,31 +2186,31 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>C$7.99, C$7.19 each at qty 3-9, in stock in Canada (Universal-Solder). Checked on the page.</t>
+          <t>One M8x90 per shoulder-to-Clavi joint, plus the elbow and wrist axles (the wrist uses an 8 mm x 6 cm bolt). The InMoov BOM lists about 15x M8x100 for the whole robot. A hardware store is cheapest. [estimate]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Joint angle sensors (x8)</t>
+          <t>ARM: Worm/gear grease</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>AS5600 magnetic encoder module</t>
+          <t>PTFE grease (Super Lube 21030 class)</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/w/wholesale-as5600-module.html</t>
+          <t>https://www.amazon.ca/s?k=super+lube+ptfe+grease</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>3.39</v>
+        <v>12</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F14" s="13">
         <f>D14*E14</f>
@@ -2218,31 +2218,31 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Absolute angle on each worm-motor output shaft. Search-page price.</t>
+          <t>Needed on the PivWorm/RotWorm and the ball races. Must not attack ABS/PLA or the plastic BBs. [estimate]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Servo bus adapters (x2)</t>
+          <t>Neck x2 + spares</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Waveshare Bus Servo Adapter (A)</t>
+          <t>Feetech STS3215 12V 30 kg-cm bus servo, 6-pack (official store)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>https://www.waveshare.com/bus-servo-adapter-a.htm</t>
+          <t>https://www.aliexpress.com/item/1005008670304643.html</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>6.99</v>
+        <v>166.42</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="13">
         <f>D15*E15</f>
@@ -2250,28 +2250,28 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>US$4.99 on waveshare.com; Canada shipping not checked.</t>
+          <t>C$160.99 + C$5.43 shipping, 4.9 stars, 232 sold. Checked on the page. Wrists moved to the owned MG996Rs (InMoov wrist uses MG996R).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Head camera</t>
+          <t>Drive base</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>EMEET C960 1080p webcam</t>
+          <t>Used hoverboard (2x 350 W hub motors + 36 V pack)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B07M6Y7355</t>
+          <t>https://www.kijiji.ca/b-city-of-toronto/hoverboard/k0c170l1700273</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>34.99</v>
+        <v>120</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>1</v>
@@ -2282,31 +2282,31 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>4.4 stars, 32.5K ratings.</t>
+          <t>C$50-150 on Kijiji Toronto (43 ads). Open it before paying: single mainboard with STM32F103RCT6/RET6 or GD32F103RCT6 only; walk away from AT32F403/413 boards. Runs EFeru FOC firmware (free).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Wrist cameras (x2)</t>
+          <t>Base power converter</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>1080p UVC wide-angle camera module</t>
+          <t>DC-DC buck 30-60 V in -&gt; 12 V, 15 A+</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/w/wholesale-wide-angle-usb-camera.html</t>
+          <t>https://www.amazon.ca/</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="13">
         <f>D17*E17</f>
@@ -2314,28 +2314,28 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Estimate. Can wait until week 3.</t>
+          <t>Estimate C$35-45. Must accept 42 V (a 36 V pack charges to 42 V), so an 18-36 V input unit will fail.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Balance / motion sensor</t>
+          <t>Casters (x2)</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>BNO085 9-axis IMU (clone)</t>
+          <t>2 in swivel casters</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/w/wholesale-bno085.html</t>
+          <t>https://www.amazon.ca/</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>17.58</v>
+        <v>20</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>1</v>
@@ -2346,31 +2346,31 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Adafruit original is C$33-40.</t>
+          <t>Estimate. Stabilize the tall torso on the hoverboard base.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Servo cables (x2 packs)</t>
+          <t>Safety + power wiring</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>5264 3-pin bus servo cable, 10-pack</t>
+          <t>E-stop button, fuses, XT60 connectors, 14 AWG wire</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/item/1005008074862037.html</t>
+          <t>https://www.amazon.ca/</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>6.72</v>
+        <v>30</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="13">
         <f>D19*E19</f>
@@ -2378,31 +2378,31 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>+ ~C$8 shipping.</t>
+          <t>Estimate. Non-negotiable for a 1.8 m robot on wheels.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Powered USB hub</t>
+          <t>Servo bus adapters (x2)</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>7-port powered USB 3.0 hub (TP-Link UH700 class)</t>
+          <t>Waveshare Bus Servo Adapter (A)</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B00OTK16FK</t>
+          <t>https://www.waveshare.com/bus-servo-adapter-a.htm</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>65</v>
+        <v>6.99</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="13">
         <f>D20*E20</f>
@@ -2410,28 +2410,28 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Checked: C$59-71 for reputable hubs.</t>
+          <t>US$4.99 on waveshare.com; Canada shipping not checked.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Head camera</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>M2/M3/M4 screw kit + 100 M3 heat-set inserts</t>
+          <t>EMEET C960 1080p webcam</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/</t>
+          <t>https://www.amazon.ca/dp/B07M6Y7355</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>27</v>
+        <v>34.99</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>1</v>
@@ -2442,31 +2442,31 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>LuKaiSen kit C$15.99 + HANGLIFE inserts C$10.99.</t>
+          <t>4.4 stars, 32.5K ratings.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Work stand clamps</t>
+          <t>Wrist cameras (x2)</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>WEN CLC424 C-clamps, 2-pack</t>
+          <t>1080p UVC wide-angle camera module</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B08SQFT9TW</t>
+          <t>https://www.aliexpress.com/w/wholesale-wide-angle-usb-camera.html</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>17.44</v>
+        <v>12</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="13">
         <f>D22*E22</f>
@@ -2474,28 +2474,28 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Holds the torso on the bench during arm bring-up.</t>
+          <t>Estimate. Can wait until week 3.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Wire + connectors</t>
+          <t>Balance / motion sensor</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Assorted wire, JST/Dupont, heat shrink</t>
+          <t>BNO085 9-axis IMU (clone)</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/</t>
+          <t>https://www.aliexpress.com/w/wholesale-bno085.html</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>35</v>
+        <v>17.58</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>1</v>
@@ -2506,53 +2506,230 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
+          <t>Adafruit original is C$33-40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Servo cables (x2 packs)</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>5264 3-pin bus servo cable, 10-pack</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/item/1005008074862037.html</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="13">
+        <f>D24*E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>+ ~C$8 shipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Powered USB hub</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>7-port powered USB 3.0 hub (TP-Link UH700 class)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B00OTK16FK</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Checked: C$59-71 for reputable hubs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>M2/M3/M4 screw kit + 100 M3 heat-set inserts</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>LuKaiSen kit C$15.99 + HANGLIFE inserts C$10.99.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Work stand clamps</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>WEN CLC424 C-clamps, 2-pack</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B08SQFT9TW</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="13">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Holds the torso on the bench during arm bring-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Wire + connectors</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Assorted wire, JST/Dupont, heat shrink</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="13">
+        <f>D28*E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
           <t>Estimate.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Phase 2 subtotal (CAD, pre-tax/shipping)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="16">
-        <f>SUM(F6:F23)</f>
-        <v/>
-      </c>
-      <c r="G24" s="15" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="16">
+        <f>SUM(F6:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Whole v1 incl. the hands cart (Phase 1 core)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="16">
+        <f>F29+BOM!F17</f>
+        <v/>
+      </c>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Under the C$1,500 budget by</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="16">
-        <f>1500-F24</f>
-        <v/>
-      </c>
-      <c r="G25" s="15" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="16">
+        <f>1500-F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>Cerebras = System-2 brain (planner, voice, replanning, success checks) in the cloud; ACT/SmolVLA motor policy runs locally at 30-50 Hz. See research brief.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A24:E24"/>
+  <mergeCells count="3">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId1"/>
@@ -2573,6 +2750,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
